--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487718_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487718_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4836</v>
+        <v>2.4548</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5766</v>
+        <v>4.2753</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0931</v>
+        <v>-1.8205</v>
       </c>
       <c r="G2" t="n">
         <v>1.5559</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2259</v>
+        <v>0.1971</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6397</v>
+        <v>0.3384</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4138</v>
+        <v>-0.1413</v>
       </c>
       <c r="V2" t="n">
         <v>0.5077</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8371</v>
+        <v>2.128</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4111</v>
+        <v>1.1108</v>
       </c>
       <c r="F3" t="n">
-        <v>1.426</v>
+        <v>1.0172</v>
       </c>
       <c r="G3" t="n">
         <v>-1.2773</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="T3" t="n">
-        <v>0.305</v>
+        <v>0.0047</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6461</v>
+        <v>0.2373</v>
       </c>
       <c r="V3" t="n">
         <v>4.1334</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. LAGNIEZ</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0939</v>
+        <v>0.0711</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1611</v>
+        <v>-0.0818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.255</v>
+        <v>0.153</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1425</v>
+        <v>-0.0159</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1244</v>
+        <v>-0.3123</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2669</v>
+        <v>0.2964</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0206</v>
+        <v>0.1024</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0206</v>
+        <v>0.0618</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.0406</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1219</v>
+        <v>-0.1183</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.145</v>
+        <v>-0.374</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2669</v>
+        <v>0.2558</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0487</v>
+        <v>-0.367</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1817</v>
+        <v>-0.1842</v>
       </c>
       <c r="U4" t="n">
-        <v>0.133</v>
+        <v>-0.1828</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>N. LAGNIEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3382</v>
+        <v>0.0393</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3821</v>
+        <v>-0.1611</v>
       </c>
       <c r="F5" t="n">
-        <v>0.044</v>
+        <v>0.2004</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0159</v>
+        <v>0.1425</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3123</v>
+        <v>-0.1244</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2964</v>
+        <v>0.2669</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1024</v>
+        <v>0.0206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0618</v>
+        <v>0.0206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1183</v>
+        <v>0.1219</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.374</v>
+        <v>-0.145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2558</v>
+        <v>0.2669</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7763</v>
+        <v>-0.1032</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4845</v>
+        <v>-0.1817</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2918</v>
+        <v>0.0785</v>
       </c>
       <c r="V5" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.86</v>
+        <v>0.0132</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0753</v>
+        <v>1.6759</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9353</v>
+        <v>-1.6627</v>
       </c>
       <c r="G6" t="n">
         <v>2.2348</v>
@@ -922,13 +922,13 @@
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8921</v>
+        <v>-1.0189</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2113</v>
+        <v>-0.6107</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6808</v>
+        <v>-0.4082</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6206</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.622</v>
+        <v>-1.7033</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8104</v>
+        <v>-2.5101</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1883</v>
+        <v>0.8068</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6121</v>
@@ -1000,13 +1000,13 @@
         <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0132</v>
+        <v>-0.0945</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6057</v>
+        <v>-0.3054</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5924</v>
+        <v>0.2109</v>
       </c>
       <c r="V7" t="n">
         <v>1.1675</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8895</v>
+        <v>-2.0931</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9803</v>
+        <v>-1.9588</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.1343</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6583</v>
+        <v>-3.1387</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9252</v>
+        <v>-1.0916</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2669</v>
+        <v>-2.0471</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-1.4229</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2101</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.2129</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0115</v>
+        <v>-1.7158</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2785</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2669</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6431</v>
+        <v>-0.4699</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6068</v>
+        <v>-0.1015</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0363</v>
+        <v>-0.3684</v>
       </c>
       <c r="V8" t="n">
-        <v>0.066</v>
+        <v>1.5155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X8" t="n">
-        <v>0.066</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4296</v>
+        <v>-2.2354</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.159</v>
+        <v>-2.3807</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2706</v>
+        <v>0.1453</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1387</v>
+        <v>-0.6583</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0916</v>
+        <v>-0.9252</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0471</v>
+        <v>0.2669</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4229</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2101</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2129</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7158</v>
+        <v>-0.0115</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.2785</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8342000000000001</v>
+        <v>0.2669</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8064</v>
+        <v>0.2972</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3017</v>
+        <v>0.2064</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5047</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5155</v>
+        <v>0.066</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.438</v>
+        <v>-2.2694</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.15</v>
+        <v>-2.121</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.288</v>
+        <v>-0.1484</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2334</v>
+        <v>-3.6394</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2076</v>
+        <v>-2.1206</v>
       </c>
       <c r="I10" t="n">
-        <v>0.441</v>
+        <v>-1.5188</v>
       </c>
       <c r="J10" t="n">
-        <v>0.123</v>
+        <v>-2.3416</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0824</v>
+        <v>-1.796</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>-0.5455</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1104</v>
+        <v>-1.2979</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.29</v>
+        <v>-0.3246</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4004</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2669</v>
+        <v>-0.5796</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3028</v>
+        <v>-0.2869</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0359</v>
+        <v>-0.2927</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6283</v>
+        <v>1.9496</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6283</v>
+        <v>-0.4982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7699</v>
+        <v>-2.3379</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6215</v>
+        <v>-1.0499</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1484</v>
+        <v>-1.288</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6394</v>
+        <v>0.2334</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1206</v>
+        <v>-0.2076</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5188</v>
+        <v>0.441</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3416</v>
+        <v>0.123</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.796</v>
+        <v>0.0824</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5455</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2979</v>
+        <v>0.1104</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3246</v>
+        <v>-0.29</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9733000000000001</v>
+        <v>0.4004</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0801</v>
+        <v>-0.1668</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7874</v>
+        <v>-0.2027</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2927</v>
+        <v>0.0359</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9496</v>
+        <v>-1.6283</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4982</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.932600000000001</v>
+        <v>-5.932699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.201399999999999</v>
+        <v>-3.2014</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.731300000000001</v>
+        <v>-2.7312</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1751</v>
+        <v>-6.175100000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-0.7249000000000001</v>
@@ -1396,7 +1396,7 @@
         <v>-1.3236</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7401</v>
+        <v>-0.74</v>
       </c>
       <c r="V12" t="n">
         <v>7.1568</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.732</v>
+        <v>11.0228</v>
       </c>
       <c r="E13" t="n">
-        <v>8.8886</v>
+        <v>8.9887</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8434</v>
+        <v>2.0342</v>
       </c>
       <c r="G13" t="n">
         <v>7.1953</v>
@@ -1468,13 +1468,13 @@
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1633</v>
+        <v>0.1276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3623</v>
+        <v>-0.2622</v>
       </c>
       <c r="U13" t="n">
-        <v>0.199</v>
+        <v>0.3898</v>
       </c>
       <c r="V13" t="n">
         <v>2.7298</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3613</v>
+        <v>4.8797</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8842</v>
+        <v>4.1845</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4771</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>2.5662</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5332</v>
+        <v>-0.0149</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1806</v>
+        <v>0.1197</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3526</v>
+        <v>-0.1346</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3658</v>
+        <v>2.2211</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8209</v>
+        <v>2.6217</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4551</v>
+        <v>-0.4006</v>
       </c>
       <c r="G15" t="n">
         <v>2.0593</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7398</v>
+        <v>0.1155</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5451</v>
+        <v>0.2557</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1947</v>
+        <v>-0.1402</v>
       </c>
       <c r="V15" t="n">
         <v>-1.506</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1205</v>
+        <v>0.6745</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-1.1321</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7521</v>
+        <v>1.8067</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7692</v>
@@ -1702,13 +1702,13 @@
         <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8136</v>
+        <v>0.3676</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9724</v>
+        <v>0.4719</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1588</v>
+        <v>-0.1043</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2821</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5864</v>
+        <v>0.623</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9992</v>
+        <v>-0.799</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5855</v>
+        <v>1.422</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1919</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0603</v>
+        <v>0.097</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3632</v>
+        <v>0.1996</v>
       </c>
       <c r="V17" t="n">
         <v>0.9418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6342</v>
+        <v>-1.1252</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0593</v>
+        <v>-0.3596</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5748</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.629</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8306</v>
+        <v>0.3396</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4856</v>
+        <v>0.1853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.345</v>
+        <v>0.1542</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.15</v>
+        <v>-1.4456</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0907</v>
+        <v>-3.0381</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0594</v>
+        <v>1.5924</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5567</v>
+        <v>-1.6109</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3304</v>
+        <v>-1.483</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2263</v>
+        <v>-0.1279</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6061</v>
+        <v>-0.7795</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0206</v>
+        <v>-0.8074</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6267</v>
+        <v>0.0279</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0494</v>
+        <v>-0.8313</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.351</v>
+        <v>-0.6756</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4004</v>
+        <v>-0.1557</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>2.3284</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4067</v>
+        <v>-0.1273</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4856</v>
+        <v>-0.2227</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.079</v>
+        <v>0.0954</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6119</v>
+        <v>-0.0955</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3171</v>
+        <v>-1.4687</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6499</v>
+        <v>-1.4911</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.967</v>
+        <v>0.0224</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1288</v>
+        <v>-0.5567</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.608</v>
+        <v>-0.3304</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7368</v>
+        <v>-0.2263</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.382</v>
+        <v>-0.6061</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5849</v>
+        <v>0.0206</v>
       </c>
       <c r="L20" t="n">
-        <v>0.203</v>
+        <v>-0.6267</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5108</v>
+        <v>0.0494</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0231</v>
+        <v>-0.351</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5339</v>
+        <v>0.4004</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4495</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0318</v>
+        <v>0.0852</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4177</v>
+        <v>0.0028</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6716</v>
+        <v>-0.6119</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.6716</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5368</v>
+        <v>-1.8994</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2382</v>
+        <v>0.1494</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7014</v>
+        <v>-2.0488</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6109</v>
+        <v>0.1288</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.483</v>
+        <v>-0.608</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1279</v>
+        <v>0.7368</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7795</v>
+        <v>-0.382</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8074</v>
+        <v>-0.5849</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0279</v>
+        <v>0.203</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8313</v>
+        <v>0.5108</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6756</v>
+        <v>-0.0231</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1557</v>
+        <v>0.5339</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2185</v>
+        <v>0.8673</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4229</v>
+        <v>0.5313</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2044</v>
+        <v>0.3359</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0955</v>
+        <v>-3.6716</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0955</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.016</v>
+        <v>-2.1522</v>
       </c>
       <c r="E22" t="n">
         <v>-1.7741</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2419</v>
+        <v>-0.3782</v>
       </c>
       <c r="G22" t="n">
         <v>0.1601</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6</v>
+        <v>0.4638</v>
       </c>
       <c r="T22" t="n">
         <v>-0.12</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7201</v>
+        <v>0.5838</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5791</v>
+        <v>-5.3972</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7191</v>
+        <v>-4.619</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8599</v>
+        <v>-0.7782</v>
       </c>
       <c r="G23" t="n">
         <v>-1.177</v>
@@ -2248,13 +2248,13 @@
         <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4424</v>
+        <v>-0.2605</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3017</v>
+        <v>-0.2016</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1406</v>
+        <v>-0.0589</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2134</v>
@@ -2284,7 +2284,7 @@
         <v>5.932799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>2.731399999999999</v>
+        <v>2.731299999999998</v>
       </c>
       <c r="F24" t="n">
         <v>3.201399999999999</v>
@@ -2293,13 +2293,13 @@
         <v>6.175000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7249999999999999</v>
+        <v>0.7250000000000003</v>
       </c>
       <c r="I24" t="n">
         <v>5.4499</v>
       </c>
       <c r="J24" t="n">
-        <v>8.082700000000001</v>
+        <v>8.082700000000003</v>
       </c>
       <c r="K24" t="n">
         <v>5.1906</v>
@@ -2326,19 +2326,19 @@
         <v>16.4928</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0635</v>
+        <v>2.0637</v>
       </c>
       <c r="T24" t="n">
-        <v>0.74</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3237</v>
+        <v>1.3235</v>
       </c>
       <c r="V24" t="n">
-        <v>-7.1567</v>
+        <v>-7.156700000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>5.550799999999999</v>
+        <v>5.5508</v>
       </c>
       <c r="X24" t="n">
         <v>-12.7074</v>
